--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/SOUTH_DAKOTA_2023.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/SOUTH_DAKOTA_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CALVILLO</t>
+          <t>Calvillo</t>
         </is>
       </c>
       <c r="C3">
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JESÚS MARÍA</t>
+          <t>Jesús María</t>
         </is>
       </c>
       <c r="C4">
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PABELLÓN DE ARTEAGA</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C5">
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C6">
@@ -449,12 +469,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAJA CALIFORNIA</t>
+          <t>Baja California</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ENSENADA</t>
+          <t>Ensenada</t>
         </is>
       </c>
       <c r="C7">
@@ -465,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MEXICALI</t>
+          <t>Mexicali</t>
         </is>
       </c>
       <c r="C8">
@@ -478,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TIJUANA</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="C9">
@@ -491,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C10">
@@ -506,12 +541,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAMPECHE</t>
+          <t>Campeche</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CARMEN</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="C11">
@@ -522,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHAMPOTÓN</t>
+          <t>Champotón</t>
         </is>
       </c>
       <c r="C12">
@@ -535,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C13">
@@ -550,12 +595,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ANGEL ALBINO CORZO</t>
+          <t>Angel Albino Corzo</t>
         </is>
       </c>
       <c r="C14">
@@ -566,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARRIAGA</t>
+          <t>Arriaga</t>
         </is>
       </c>
       <c r="C15">
@@ -579,9 +629,14 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EL PORVENIR</t>
+          <t>El Porvenir</t>
         </is>
       </c>
       <c r="C16">
@@ -592,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FRONTERA COMALAPA</t>
+          <t>Frontera Comalapa</t>
         </is>
       </c>
       <c r="C17">
@@ -605,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HUIXTLA</t>
+          <t>Huixtla</t>
         </is>
       </c>
       <c r="C18">
@@ -618,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JIQUIPILAS</t>
+          <t>Jiquipilas</t>
         </is>
       </c>
       <c r="C19">
@@ -631,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA TRINITARIA</t>
+          <t>La Trinitaria</t>
         </is>
       </c>
       <c r="C20">
@@ -644,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAS MARGARITAS</t>
+          <t>Las Margaritas</t>
         </is>
       </c>
       <c r="C21">
@@ -657,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MARQUÉS DE COMILLAS</t>
+          <t>Marqués De Comillas</t>
         </is>
       </c>
       <c r="C22">
@@ -670,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>METAPA</t>
+          <t>Metapa</t>
         </is>
       </c>
       <c r="C23">
@@ -683,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MOTOZINTLA</t>
+          <t>Motozintla</t>
         </is>
       </c>
       <c r="C24">
@@ -696,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OCOSINGO</t>
+          <t>Ocosingo</t>
         </is>
       </c>
       <c r="C25">
@@ -709,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OCOTEPEC</t>
+          <t>Ocotepec</t>
         </is>
       </c>
       <c r="C26">
@@ -722,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PALENQUE</t>
+          <t>Palenque</t>
         </is>
       </c>
       <c r="C27">
@@ -735,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAN CRISTÓBAL DE LAS CASAS</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C28">
@@ -748,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SILTEPEC</t>
+          <t>Siltepec</t>
         </is>
       </c>
       <c r="C29">
@@ -761,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TAPACHULA</t>
+          <t>Tapachula</t>
         </is>
       </c>
       <c r="C30">
@@ -774,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VILLAFLORES</t>
+          <t>Villaflores</t>
         </is>
       </c>
       <c r="C31">
@@ -787,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C32">
@@ -802,12 +937,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CAMARGO</t>
+          <t>Camargo</t>
         </is>
       </c>
       <c r="C33">
@@ -818,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="C34">
@@ -831,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GRAN MORELOS</t>
+          <t>Gran Morelos</t>
         </is>
       </c>
       <c r="C35">
@@ -844,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GUADALUPE Y CALVO</t>
+          <t>Guadalupe Y Calvo</t>
         </is>
       </c>
       <c r="C36">
@@ -857,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GÓMEZ FARÍAS</t>
+          <t>Gómez Farías</t>
         </is>
       </c>
       <c r="C37">
@@ -870,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JUÁREZ</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="C38">
@@ -883,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NAMIQUIPA</t>
+          <t>Namiquipa</t>
         </is>
       </c>
       <c r="C39">
@@ -896,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C40">
@@ -911,12 +1081,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AZCAPOTZALCO</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="C41">
@@ -927,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BENITO JUÁREZ</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="C42">
@@ -940,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C43">
@@ -953,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GUSTAVO A. MADERO</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="C44">
@@ -966,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>XOCHIMILCO</t>
+          <t>Xochimilco</t>
         </is>
       </c>
       <c r="C45">
@@ -979,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ÁLVARO OBREGÓN</t>
+          <t>Álvaro Obregón</t>
         </is>
       </c>
       <c r="C46">
@@ -992,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C47">
@@ -1007,12 +1207,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COAHUILA DE ZARAGOZA</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FRANCISCO I. MADERO</t>
+          <t>Francisco I. Madero</t>
         </is>
       </c>
       <c r="C48">
@@ -1023,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MONCLOVA</t>
+          <t>Monclova</t>
         </is>
       </c>
       <c r="C49">
@@ -1036,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MÚZQUIZ</t>
+          <t>Múzquiz</t>
         </is>
       </c>
       <c r="C50">
@@ -1049,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>San Pedro</t>
         </is>
       </c>
       <c r="C51">
@@ -1062,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TORREÓN</t>
+          <t>Torreón</t>
         </is>
       </c>
       <c r="C52">
@@ -1075,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C53">
@@ -1090,12 +1315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CANATLÁN</t>
+          <t>Canatlán</t>
         </is>
       </c>
       <c r="C54">
@@ -1106,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GÓMEZ PALACIO</t>
+          <t>Gómez Palacio</t>
         </is>
       </c>
       <c r="C55">
@@ -1119,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VICENTE GUERRERO</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C56">
@@ -1132,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C57">
@@ -1147,12 +1387,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ESTADO DE MÉXICO</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ALMOLOYA DE JUÁREZ</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C58">
@@ -1163,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ATLACOMULCO</t>
+          <t>Atlacomulco</t>
         </is>
       </c>
       <c r="C59">
@@ -1176,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CHALCO</t>
+          <t>Chalco</t>
         </is>
       </c>
       <c r="C60">
@@ -1189,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ECATEPEC DE MORELOS</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C61">
@@ -1202,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SAN FELIPE DEL PROGRESO</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C62">
@@ -1215,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TEJUPILCO</t>
+          <t>Tejupilco</t>
         </is>
       </c>
       <c r="C63">
@@ -1228,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TIMILPAN</t>
+          <t>Timilpan</t>
         </is>
       </c>
       <c r="C64">
@@ -1241,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA DE BAZ</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C65">
@@ -1254,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TOLUCA</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="C66">
@@ -1267,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TULTEPEC</t>
+          <t>Tultepec</t>
         </is>
       </c>
       <c r="C67">
@@ -1280,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VILLA VICTORIA</t>
+          <t>Villa Victoria</t>
         </is>
       </c>
       <c r="C68">
@@ -1293,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C69">
@@ -1308,12 +1603,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CELAYA</t>
+          <t>Celaya</t>
         </is>
       </c>
       <c r="C70">
@@ -1324,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DOLORES HIDALGO CUNA DE LA INDEPENDENCIA NACIONAL</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C71">
@@ -1337,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IRAPUATO</t>
+          <t>Irapuato</t>
         </is>
       </c>
       <c r="C72">
@@ -1350,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LEÓN</t>
+          <t>León</t>
         </is>
       </c>
       <c r="C73">
@@ -1363,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MANUEL DOBLADO</t>
+          <t>Manuel Doblado</t>
         </is>
       </c>
       <c r="C74">
@@ -1376,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PUEBLO NUEVO</t>
+          <t>Pueblo Nuevo</t>
         </is>
       </c>
       <c r="C75">
@@ -1389,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PURÍSIMA DEL RINCÓN</t>
+          <t>Purísima Del Rincón</t>
         </is>
       </c>
       <c r="C76">
@@ -1402,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PÉNJAMO</t>
+          <t>Pénjamo</t>
         </is>
       </c>
       <c r="C77">
@@ -1415,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SALAMANCA</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="C78">
@@ -1428,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DEL RINCÓN</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C79">
@@ -1441,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SAN JOSÉ ITURBIDE</t>
+          <t>San José Iturbide</t>
         </is>
       </c>
       <c r="C80">
@@ -1454,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SAN LUIS DE LA PAZ</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C81">
@@ -1467,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SANTA CRUZ DE JUVENTINO ROSAS</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C82">
@@ -1480,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C83">
@@ -1495,12 +1855,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ACAPULCO DE JUÁREZ</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C84">
@@ -1511,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AHUACUOTZINGO</t>
+          <t>Ahuacuotzingo</t>
         </is>
       </c>
       <c r="C85">
@@ -1524,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ATOYAC DE ÁLVAREZ</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C86">
@@ -1537,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>COPALILLO</t>
+          <t>Copalillo</t>
         </is>
       </c>
       <c r="C87">
@@ -1550,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>COYUCA DE CATALÁN</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C88">
@@ -1563,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HUITZUCO DE LOS FIGUEROA</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C89">
@@ -1576,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IGUALAPA</t>
+          <t>Igualapa</t>
         </is>
       </c>
       <c r="C90">
@@ -1589,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LEONARDO BRAVO</t>
+          <t>Leonardo Bravo</t>
         </is>
       </c>
       <c r="C91">
@@ -1602,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PILCAYA</t>
+          <t>Pilcaya</t>
         </is>
       </c>
       <c r="C92">
@@ -1615,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>QUECHULTENANGO</t>
+          <t>Quechultenango</t>
         </is>
       </c>
       <c r="C93">
@@ -1628,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SAN MIGUEL TOTOLAPAN</t>
+          <t>San Miguel Totolapan</t>
         </is>
       </c>
       <c r="C94">
@@ -1641,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TLAPEHUALA</t>
+          <t>Tlapehuala</t>
         </is>
       </c>
       <c r="C95">
@@ -1654,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TÉCPAN DE GALEANA</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C96">
@@ -1667,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZIHUATANEJO DE AZUETA</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C97">
@@ -1680,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZIRÁNDARO</t>
+          <t>Zirándaro</t>
         </is>
       </c>
       <c r="C98">
@@ -1693,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C99">
@@ -1708,12 +2143,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ATOTONILCO EL GRANDE</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C100">
@@ -1724,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IXMIQUILPAN</t>
+          <t>Ixmiquilpan</t>
         </is>
       </c>
       <c r="C101">
@@ -1737,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>Metepec</t>
         </is>
       </c>
       <c r="C102">
@@ -1750,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PACHUCA DE SOTO</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C103">
@@ -1763,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TULANCINGO DE BRAVO</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C104">
@@ -1776,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>XOCHIATIPAN</t>
+          <t>Xochiatipan</t>
         </is>
       </c>
       <c r="C105">
@@ -1789,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C106">
@@ -1804,12 +2269,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JALISCO</t>
+          <t>Jalisco</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ATOTONILCO EL ALTO</t>
+          <t>Atotonilco El Alto</t>
         </is>
       </c>
       <c r="C107">
@@ -1820,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AYOTLÁN</t>
+          <t>Ayotlán</t>
         </is>
       </c>
       <c r="C108">
@@ -1833,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AYUTLA</t>
+          <t>Ayutla</t>
         </is>
       </c>
       <c r="C109">
@@ -1846,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>COLOTLÁN</t>
+          <t>Colotlán</t>
         </is>
       </c>
       <c r="C110">
@@ -1859,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DEGOLLADO</t>
+          <t>Degollado</t>
         </is>
       </c>
       <c r="C111">
@@ -1872,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="C112">
@@ -1885,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JESÚS MARÍA</t>
+          <t>Jesús María</t>
         </is>
       </c>
       <c r="C113">
@@ -1898,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JUCHITLÁN</t>
+          <t>Juchitlán</t>
         </is>
       </c>
       <c r="C114">
@@ -1911,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LA BARCA</t>
+          <t>La Barca</t>
         </is>
       </c>
       <c r="C115">
@@ -1924,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>OCOTLÁN</t>
+          <t>Ocotlán</t>
         </is>
       </c>
       <c r="C116">
@@ -1937,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PONCITLÁN</t>
+          <t>Poncitlán</t>
         </is>
       </c>
       <c r="C117">
@@ -1950,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SAN DIEGO DE ALEJANDRÍA</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C118">
@@ -1963,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SAN MIGUEL EL ALTO</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C119">
@@ -1976,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TALA</t>
+          <t>Tala</t>
         </is>
       </c>
       <c r="C120">
@@ -1989,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TEPATITLÁN DE MORELOS</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C121">
@@ -2002,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TEUCHITLÁN</t>
+          <t>Teuchitlán</t>
         </is>
       </c>
       <c r="C122">
@@ -2015,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TLAJOMULCO DE ZÚÑIGA</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C123">
@@ -2028,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TONALÁ</t>
+          <t>Tonalá</t>
         </is>
       </c>
       <c r="C124">
@@ -2041,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>UNIÓN DE TULA</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C125">
@@ -2054,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ZAPOPAN</t>
+          <t>Zapopan</t>
         </is>
       </c>
       <c r="C126">
@@ -2067,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C127">
@@ -2082,12 +2647,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>APATZINGÁN</t>
+          <t>Apatzingán</t>
         </is>
       </c>
       <c r="C128">
@@ -2098,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AQUILA</t>
+          <t>Aquila</t>
         </is>
       </c>
       <c r="C129">
@@ -2111,9 +2681,14 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>COALCOMÁN DE VÁZQUEZ PALLARES</t>
+          <t>Coalcomán De Vázquez Pallares</t>
         </is>
       </c>
       <c r="C130">
@@ -2124,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>JUNGAPEO</t>
+          <t>Jungapeo</t>
         </is>
       </c>
       <c r="C131">
@@ -2137,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LA PIEDAD</t>
+          <t>La Piedad</t>
         </is>
       </c>
       <c r="C132">
@@ -2150,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LÁZARO CÁRDENAS</t>
+          <t>Lázaro Cárdenas</t>
         </is>
       </c>
       <c r="C133">
@@ -2163,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t>Morelia</t>
         </is>
       </c>
       <c r="C134">
@@ -2176,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PURÉPERO</t>
+          <t>Purépero</t>
         </is>
       </c>
       <c r="C135">
@@ -2189,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TARÍMBARO</t>
+          <t>Tarímbaro</t>
         </is>
       </c>
       <c r="C136">
@@ -2202,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TLAZAZALCA</t>
+          <t>Tlazazalca</t>
         </is>
       </c>
       <c r="C137">
@@ -2215,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TUZANTLA</t>
+          <t>Tuzantla</t>
         </is>
       </c>
       <c r="C138">
@@ -2228,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>URUAPAN</t>
+          <t>Uruapan</t>
         </is>
       </c>
       <c r="C139">
@@ -2241,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>VENUSTIANO CARRANZA</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="C140">
@@ -2254,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C141">
@@ -2269,12 +2899,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>Morelos</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CUERNAVACA</t>
+          <t>Cuernavaca</t>
         </is>
       </c>
       <c r="C142">
@@ -2285,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MIACATLÁN</t>
+          <t>Miacatlán</t>
         </is>
       </c>
       <c r="C143">
@@ -2298,9 +2933,14 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C144">
@@ -2313,12 +2953,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NAYARIT</t>
+          <t>Nayarit</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ACAPONETA</t>
+          <t>Acaponeta</t>
         </is>
       </c>
       <c r="C145">
@@ -2329,9 +2969,14 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAN BLAS</t>
+          <t>San Blas</t>
         </is>
       </c>
       <c r="C146">
@@ -2342,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SANTIAGO IXCUINTLA</t>
+          <t>Santiago Ixcuintla</t>
         </is>
       </c>
       <c r="C147">
@@ -2355,9 +3005,14 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TEPIC</t>
+          <t>Tepic</t>
         </is>
       </c>
       <c r="C148">
@@ -2368,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TUXPAN</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C149">
@@ -2381,9 +3041,14 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C150">
@@ -2396,12 +3061,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NUEVO LEÓN</t>
+          <t>Nuevo León</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MONTERREY</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="C151">
@@ -2412,9 +3077,14 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C152">
@@ -2427,12 +3097,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HEROICA CIUDAD DE TLAXIACO</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C153">
@@ -2443,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HUAJUAPAN DE LEÓN</t>
+          <t>Huajuapan De León</t>
         </is>
       </c>
       <c r="C154">
@@ -2456,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SAN AGUSTÍN LOXICHA</t>
+          <t>San Agustín Loxicha</t>
         </is>
       </c>
       <c r="C155">
@@ -2469,9 +3149,14 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SAN ANTONINO EL ALTO</t>
+          <t>San Antonino El Alto</t>
         </is>
       </c>
       <c r="C156">
@@ -2482,9 +3167,14 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SAN ANTONIO TEPETLAPA</t>
+          <t>San Antonio Tepetlapa</t>
         </is>
       </c>
       <c r="C157">
@@ -2495,9 +3185,14 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SAN CARLOS YAUTEPEC</t>
+          <t>San Carlos Yautepec</t>
         </is>
       </c>
       <c r="C158">
@@ -2508,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SAN LORENZO TEXMELÚCAN</t>
+          <t>San Lorenzo Texmelúcan</t>
         </is>
       </c>
       <c r="C159">
@@ -2521,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SAN MIGUEL ALOÁPAM</t>
+          <t>San Miguel Aloápam</t>
         </is>
       </c>
       <c r="C160">
@@ -2534,9 +3239,14 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SAN PEDRO TOTOLÁPAM</t>
+          <t>San Pedro Totolápam</t>
         </is>
       </c>
       <c r="C161">
@@ -2547,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SANTA MARÍA XADANI</t>
+          <t>Santa María Xadani</t>
         </is>
       </c>
       <c r="C162">
@@ -2560,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SANTIAGO PINOTEPA NACIONAL</t>
+          <t>Santiago Pinotepa Nacional</t>
         </is>
       </c>
       <c r="C163">
@@ -2573,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO TONALÁ</t>
+          <t>Santo Domingo Tonalá</t>
         </is>
       </c>
       <c r="C164">
@@ -2586,9 +3311,14 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>VILLA DE ETLA</t>
+          <t>Villa De Etla</t>
         </is>
       </c>
       <c r="C165">
@@ -2599,9 +3329,14 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ZIMATLÁN DE ÁLVAREZ</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C166">
@@ -2612,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C167">
@@ -2627,12 +3367,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>AJALPAN</t>
+          <t>Ajalpan</t>
         </is>
       </c>
       <c r="C168">
@@ -2643,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CHICHIQUILA</t>
+          <t>Chichiquila</t>
         </is>
       </c>
       <c r="C169">
@@ -2656,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>COATZINGO</t>
+          <t>Coatzingo</t>
         </is>
       </c>
       <c r="C170">
@@ -2669,9 +3419,14 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CUAUTLANCINGO</t>
+          <t>Cuautlancingo</t>
         </is>
       </c>
       <c r="C171">
@@ -2682,9 +3437,14 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>QUECHOLAC</t>
+          <t>Quecholac</t>
         </is>
       </c>
       <c r="C172">
@@ -2695,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>QUIMIXTLÁN</t>
+          <t>Quimixtlán</t>
         </is>
       </c>
       <c r="C173">
@@ -2708,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SAN MARTÍN TEXMELUCAN</t>
+          <t>San Martín Texmelucan</t>
         </is>
       </c>
       <c r="C174">
@@ -2721,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TEHUACÁN</t>
+          <t>Tehuacán</t>
         </is>
       </c>
       <c r="C175">
@@ -2734,9 +3509,14 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TEOTLALCO</t>
+          <t>Teotlalco</t>
         </is>
       </c>
       <c r="C176">
@@ -2747,9 +3527,14 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TEZIUTLÁN</t>
+          <t>Teziutlán</t>
         </is>
       </c>
       <c r="C177">
@@ -2760,9 +3545,14 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>VICENTE GUERRERO</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C178">
@@ -2773,9 +3563,14 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>XICOTEPEC</t>
+          <t>Xicotepec</t>
         </is>
       </c>
       <c r="C179">
@@ -2786,9 +3581,14 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ZACAPOAXTLA</t>
+          <t>Zacapoaxtla</t>
         </is>
       </c>
       <c r="C180">
@@ -2799,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ZACATLÁN</t>
+          <t>Zacatlán</t>
         </is>
       </c>
       <c r="C181">
@@ -2812,9 +3617,14 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="C182">
@@ -2825,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C183">
@@ -2840,12 +3655,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AMEALCO DE BONFIL</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C184">
@@ -2856,9 +3671,14 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PEDRO ESCOBEDO</t>
+          <t>Pedro Escobedo</t>
         </is>
       </c>
       <c r="C185">
@@ -2869,9 +3689,14 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="C186">
@@ -2882,9 +3707,14 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C187">
@@ -2897,12 +3727,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CIUDAD VALLES</t>
+          <t>Ciudad Valles</t>
         </is>
       </c>
       <c r="C188">
@@ -2913,9 +3743,14 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C189">
@@ -2926,9 +3761,14 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="C190">
@@ -2939,9 +3779,14 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SANTA MARÍA DEL RÍO</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C191">
@@ -2952,9 +3797,14 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TAMASOPO</t>
+          <t>Tamasopo</t>
         </is>
       </c>
       <c r="C192">
@@ -2965,9 +3815,14 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TAMUÍN</t>
+          <t>Tamuín</t>
         </is>
       </c>
       <c r="C193">
@@ -2978,9 +3833,14 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TIERRA NUEVA</t>
+          <t>Tierra Nueva</t>
         </is>
       </c>
       <c r="C194">
@@ -2991,9 +3851,14 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>VILLA DE RAMOS</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C195">
@@ -3004,9 +3869,14 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C196">
@@ -3019,12 +3889,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SINALOA</t>
+          <t>Sinaloa</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SALVADOR ALVARADO</t>
+          <t>Salvador Alvarado</t>
         </is>
       </c>
       <c r="C197">
@@ -3035,9 +3905,14 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C198">
@@ -3050,12 +3925,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SONORA</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CAJEME</t>
+          <t>Cajeme</t>
         </is>
       </c>
       <c r="C199">
@@ -3066,9 +3941,14 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C200">
@@ -3081,12 +3961,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TAMAULIPAS</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ABASOLO</t>
+          <t>Abasolo</t>
         </is>
       </c>
       <c r="C201">
@@ -3097,9 +3977,14 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ALTAMIRA</t>
+          <t>Altamira</t>
         </is>
       </c>
       <c r="C202">
@@ -3110,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>EL MANTE</t>
+          <t>El Mante</t>
         </is>
       </c>
       <c r="C203">
@@ -3123,9 +4013,14 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>NUEVO LAREDO</t>
+          <t>Nuevo Laredo</t>
         </is>
       </c>
       <c r="C204">
@@ -3136,9 +4031,14 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>VICTORIA</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C205">
@@ -3149,9 +4049,14 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C206">
@@ -3164,12 +4069,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ATZALAN</t>
+          <t>Atzalan</t>
         </is>
       </c>
       <c r="C207">
@@ -3180,9 +4085,14 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>CARRILLO PUERTO</t>
+          <t>Carrillo Puerto</t>
         </is>
       </c>
       <c r="C208">
@@ -3193,9 +4103,14 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>COACOATZINTLA</t>
+          <t>Coacoatzintla</t>
         </is>
       </c>
       <c r="C209">
@@ -3206,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>IGNACIO DE LA LLAVE</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C210">
@@ -3219,9 +4139,14 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>IXHUACÁN DE LOS REYES</t>
+          <t>Ixhuacán De Los Reyes</t>
         </is>
       </c>
       <c r="C211">
@@ -3232,9 +4157,14 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MINATITLÁN</t>
+          <t>Minatitlán</t>
         </is>
       </c>
       <c r="C212">
@@ -3245,9 +4175,14 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>OMEALCA</t>
+          <t>Omealca</t>
         </is>
       </c>
       <c r="C213">
@@ -3258,9 +4193,14 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ORIZABA</t>
+          <t>Orizaba</t>
         </is>
       </c>
       <c r="C214">
@@ -3271,9 +4211,14 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PASO DE OVEJAS</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C215">
@@ -3284,9 +4229,14 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SOLEDAD DE DOBLADO</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C216">
@@ -3297,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>TIERRA BLANCA</t>
+          <t>Tierra Blanca</t>
         </is>
       </c>
       <c r="C217">
@@ -3310,9 +4265,14 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>TLAPACOYAN</t>
+          <t>Tlapacoyan</t>
         </is>
       </c>
       <c r="C218">
@@ -3323,9 +4283,14 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>VERACRUZ</t>
+          <t>Veracruz</t>
         </is>
       </c>
       <c r="C219">
@@ -3336,9 +4301,14 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C220">
@@ -3351,12 +4321,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>CHALCHIHUITES</t>
+          <t>Chalchihuites</t>
         </is>
       </c>
       <c r="C221">
@@ -3367,9 +4337,14 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>NORIA DE ÁNGELES</t>
+          <t>Noria De Ángeles</t>
         </is>
       </c>
       <c r="C222">
@@ -3380,9 +4355,14 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>VILLA DE COS</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C223">
@@ -3393,9 +4373,14 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C224">
@@ -3408,7 +4393,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C225">
@@ -3416,41 +4401,6 @@
       </c>
       <c r="D225">
         <v>1</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
